--- a/data/trans_dic/P1805_2016_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1805_2016_2023-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,34</t>
+          <t>1,24; 3,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,64</t>
+          <t>1,31; 4,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,7</t>
+          <t>3,07; 5,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,24</t>
+          <t>2,31; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,3</t>
+          <t>2,56; 4,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,01</t>
+          <t>2,17; 3,76</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,41</t>
+          <t>1,26; 2,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,15</t>
+          <t>2,55; 4,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,66</t>
+          <t>2,88; 4,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,45</t>
+          <t>3,25; 4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,3</t>
+          <t>2,21; 3,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,03</t>
+          <t>3,15; 4,38</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,82</t>
+          <t>0,73; 3,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,53</t>
+          <t>2,48; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,34</t>
+          <t>1,64; 4,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,21</t>
+          <t>4,76; 8,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,13</t>
+          <t>1,38; 3,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,77</t>
+          <t>3,93; 6,34</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,3</t>
+          <t>1,39; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,07</t>
+          <t>2,63; 4,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 4,39</t>
+          <t>3,12; 4,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,69</t>
+          <t>3,62; 4,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,26</t>
+          <t>2,43; 3,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,15</t>
+          <t>3,36; 4,28</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>39889</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8767; 25208</t>
+          <t>9361; 25638</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7760; 23905</t>
+          <t>7601; 23679</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29508; 56699</t>
+          <t>30527; 57875</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17110; 31981</t>
+          <t>18996; 34171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44257; 75200</t>
+          <t>44761; 76460</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29124; 50911</t>
+          <t>30357; 52650</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>75577</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78638</t>
+          <t>86423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>149251</t>
+          <t>162000</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26369; 49995</t>
+          <t>26073; 50291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47377; 95124</t>
+          <t>56768; 100929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58368; 92680</t>
+          <t>57301; 93693</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55288; 99623</t>
+          <t>70481; 106113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90710; 134262</t>
+          <t>89845; 131754</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114237; 182340</t>
+          <t>138562; 192969</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42056</t>
+          <t>44993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68773</t>
+          <t>72469</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3864; 15444</t>
+          <t>3976; 16574</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18142; 42203</t>
+          <t>17671; 42454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9054; 23809</t>
+          <t>8998; 24498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30854; 54238</t>
+          <t>35007; 60036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14853; 34301</t>
+          <t>15137; 34132</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54759; 88545</t>
+          <t>56911; 91679</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46442; 77803</t>
+          <t>46790; 77224</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82228; 140464</t>
+          <t>92455; 144846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109658; 155162</t>
+          <t>110045; 156777</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113595; 171157</t>
+          <t>135049; 183993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>167139; 225001</t>
+          <t>167894; 225615</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>216167; 294640</t>
+          <t>243679; 310319</t>
         </is>
       </c>
     </row>
